--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487948_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487948_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>F. CABRERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2681</v>
+        <v>8.461399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.34</v>
+        <v>5.4314</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9282</v>
+        <v>3.03</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2589</v>
+        <v>4.703</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7201</v>
+        <v>1.7835</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4611</v>
+        <v>2.9195</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5509</v>
+        <v>4.7985</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7083</v>
+        <v>1.5001</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1574</v>
+        <v>3.2985</v>
       </c>
       <c r="M2" t="n">
-        <v>0.708</v>
+        <v>-0.0955</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0118</v>
+        <v>0.2834</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6962</v>
+        <v>-0.379</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1234</v>
+        <v>1.5096</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0925</v>
+        <v>0.5645</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0308</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.877</v>
+        <v>0.2666</v>
       </c>
       <c r="W2" t="n">
-        <v>2.877</v>
+        <v>0.2666</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3103</v>
+        <v>8.3841</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6518</v>
+        <v>5.7537</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6585</v>
+        <v>2.6304</v>
       </c>
       <c r="G3" t="n">
         <v>3.6185</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.899</v>
+        <v>0.9728</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1176</v>
+        <v>0.2194</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7814</v>
+        <v>0.7533</v>
       </c>
       <c r="V3" t="n">
         <v>1.8107</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.8059</v>
+        <v>8.287599999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6257</v>
+        <v>5.1176</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1803</v>
+        <v>3.17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6349</v>
+        <v>4.2589</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7958</v>
+        <v>4.7201</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8391</v>
+        <v>-0.4611</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2246</v>
+        <v>3.5509</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3273</v>
+        <v>4.7083</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8972</v>
+        <v>-1.1574</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5896</v>
+        <v>0.708</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5315</v>
+        <v>0.0118</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0581</v>
+        <v>0.6962</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.1805</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.1893</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.1805</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.4485</v>
+        <v>2.1428</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8591</v>
+        <v>0.8701</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5894</v>
+        <v>1.2727</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5331</v>
+        <v>2.877</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>2.877</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. CABRERA</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7.7836</v>
+        <v>7.4899</v>
       </c>
       <c r="E5" t="n">
-        <v>4.922</v>
+        <v>6.422</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8615</v>
+        <v>1.0679</v>
       </c>
       <c r="G5" t="n">
-        <v>4.703</v>
+        <v>4.6349</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7835</v>
+        <v>1.7958</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9195</v>
+        <v>2.8391</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7985</v>
+        <v>6.2246</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5001</v>
+        <v>2.3273</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2985</v>
+        <v>3.8972</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0955</v>
+        <v>-1.5896</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2834</v>
+        <v>-0.5315</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.379</v>
+        <v>-1.0581</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
         <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8318</v>
+        <v>1.1325</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0552</v>
+        <v>0.6553</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7766</v>
+        <v>0.4771</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9744</v>
+        <v>4.4195</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1562</v>
+        <v>2.6859</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1819</v>
+        <v>1.7336</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4446</v>
+        <v>3.7589</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8647</v>
+        <v>0.9351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5799</v>
+        <v>2.8238</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1626</v>
+        <v>4.7297</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8569</v>
+        <v>0.9893</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3057</v>
+        <v>3.7404</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.718</v>
+        <v>-0.9708</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0078</v>
+        <v>-0.0542</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7258</v>
+        <v>-0.9166</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8073</v>
+        <v>0.6011</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0463</v>
+        <v>0.2754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.239</v>
+        <v>0.3257</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0704</v>
+        <v>-0.337</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1367</v>
+        <v>-0.337</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7593</v>
+        <v>4.2968</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2784</v>
+        <v>0.0945</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4809</v>
+        <v>4.2022</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7589</v>
+        <v>0.7097</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9351</v>
+        <v>0.1988</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8238</v>
+        <v>0.5109</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7297</v>
+        <v>-0.1363</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9893</v>
+        <v>0.4508</v>
       </c>
       <c r="L7" t="n">
-        <v>3.7404</v>
+        <v>-0.5871</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9708</v>
+        <v>0.846</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0542</v>
+        <v>-0.252</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9166</v>
+        <v>1.098</v>
       </c>
       <c r="P7" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0591</v>
+        <v>1.3096</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.132</v>
+        <v>0.213</v>
       </c>
       <c r="U7" t="n">
-        <v>0.073</v>
+        <v>1.0965</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.337</v>
+        <v>1.8811</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5243</v>
+        <v>4.0233</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3129</v>
+        <v>4.9525</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8372</v>
+        <v>-0.9292</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7097</v>
+        <v>2.4446</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1988</v>
+        <v>1.8647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5109</v>
+        <v>0.5799</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1363</v>
+        <v>4.1626</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4508</v>
+        <v>1.8569</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5871</v>
+        <v>2.3057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.846</v>
+        <v>-1.718</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.252</v>
+        <v>0.0078</v>
       </c>
       <c r="O8" t="n">
-        <v>1.098</v>
+        <v>-1.7258</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5371</v>
+        <v>0.8562</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1944</v>
+        <v>0.8425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7315</v>
+        <v>0.0137</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8811</v>
+        <v>-0.0704</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X8" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8589</v>
+        <v>2.2754</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9926</v>
+        <v>0.0541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8663</v>
+        <v>2.2213</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8088</v>
+        <v>-1.0691</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7111</v>
+        <v>1.7338</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0977</v>
+        <v>-2.8028</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7133</v>
+        <v>0.645</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9945000000000001</v>
+        <v>1.722</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2812</v>
+        <v>-1.077</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0955</v>
+        <v>-1.7141</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2834</v>
+        <v>0.0118</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.379</v>
+        <v>-1.7258</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.784</v>
+        <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5399</v>
+        <v>0.8865</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1549</v>
+        <v>0.4002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.385</v>
+        <v>0.4863</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5331</v>
+        <v>0.674</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3733</v>
+        <v>2.1948</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3534</v>
+        <v>1.0758</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7267</v>
+        <v>1.119</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0691</v>
+        <v>-0.8088</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7338</v>
+        <v>-0.7111</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8028</v>
+        <v>-0.0977</v>
       </c>
       <c r="J10" t="n">
-        <v>0.645</v>
+        <v>-0.7133</v>
       </c>
       <c r="K10" t="n">
-        <v>1.722</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.077</v>
+        <v>0.2812</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7141</v>
+        <v>-0.0955</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0118</v>
+        <v>0.2834</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7258</v>
+        <v>-0.379</v>
       </c>
       <c r="P10" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1893</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.784</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.7751</v>
-      </c>
       <c r="S10" t="n">
-        <v>0.9844000000000001</v>
+        <v>1.8758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0072</v>
+        <v>1.2381</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9917</v>
+        <v>0.6377</v>
       </c>
       <c r="V10" t="n">
-        <v>0.674</v>
+        <v>0.5331</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X10" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1074</v>
+        <v>-0.0513</v>
       </c>
       <c r="E11" t="n">
         <v>-0.147</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0396</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>0.2516</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5572</v>
+        <v>-0.5011</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.37</v>
+        <v>-0.3139</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.828</v>
+        <v>-1.5119</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4359</v>
+        <v>-2.2321</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6079</v>
+        <v>0.7202</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9873</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8318</v>
+        <v>-0.5157</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4992</v>
+        <v>-0.2954</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3326</v>
+        <v>-0.2203</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1929</v>
+        <v>-1.7397</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5948</v>
+        <v>-1.0854</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5981</v>
+        <v>-0.6543</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0146</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4449</v>
+        <v>0.0083</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.312</v>
+        <v>0.1974</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1329</v>
+        <v>-0.1891</v>
       </c>
       <c r="V13" t="n">
         <v>-0.337</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>46.5298</v>
+        <v>46.52990000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>28.1227</v>
+        <v>28.123</v>
       </c>
       <c r="F14" t="n">
-        <v>18.4071</v>
+        <v>18.4068</v>
       </c>
       <c r="G14" t="n">
         <v>19.5003</v>
@@ -1528,10 +1528,10 @@
         <v>10.524</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.0302</v>
+        <v>-5.030200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1177</v>
+        <v>0.1176999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-5.148</v>
@@ -1549,16 +1549,16 @@
         <v>10.2784</v>
       </c>
       <c r="T14" t="n">
-        <v>4.9936</v>
+        <v>4.993300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>5.284899999999999</v>
+        <v>5.2848</v>
       </c>
       <c r="V14" t="n">
         <v>7.831199999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>9.501099999999999</v>
+        <v>9.501100000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-1.6698</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6969</v>
+        <v>2.9496</v>
       </c>
       <c r="E15" t="n">
         <v>3.7957</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0988</v>
+        <v>-0.8461</v>
       </c>
       <c r="G15" t="n">
         <v>3.7972</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2301</v>
+        <v>-0.9774</v>
       </c>
       <c r="T15" t="n">
         <v>-0.312</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9181</v>
+        <v>-0.6654</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2666</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5712</v>
+        <v>0.9225</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1156</v>
+        <v>2.5231</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5444</v>
+        <v>-1.6006</v>
       </c>
       <c r="G16" t="n">
         <v>1.3633</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3868</v>
+        <v>-2.0355</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5599</v>
+        <v>-1.1525</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8269</v>
+        <v>-0.883</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0566</v>
+        <v>-0.8633</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3188</v>
+        <v>-1.0132</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2622</v>
+        <v>0.1499</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1447</v>
@@ -1858,13 +1858,13 @@
         <v>0.3964</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3172</v>
+        <v>-0.1239</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4992</v>
+        <v>-0.1936</v>
       </c>
       <c r="U18" t="n">
-        <v>0.182</v>
+        <v>0.0696</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.73</v>
+        <v>-3.3401</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.635</v>
+        <v>-2.3294</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.095</v>
+        <v>-1.0108</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4808</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2779</v>
+        <v>0.112</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3744</v>
+        <v>-0.0688</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0965</v>
+        <v>0.1807</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1962</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9539</v>
+        <v>-5.0525</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5704</v>
+        <v>-1.9778</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3835</v>
+        <v>-3.0746</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0999</v>
@@ -2014,13 +2014,13 @@
         <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5853</v>
+        <v>-1.6839</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2017</v>
+        <v>-0.6091</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3837</v>
+        <v>-1.0748</v>
       </c>
       <c r="V20" t="n">
         <v>0.5331</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2817</v>
+        <v>-5.3281</v>
       </c>
       <c r="E21" t="n">
-        <v>0.584</v>
+        <v>-3.5176</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.8657</v>
+        <v>-1.8104</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0588</v>
+        <v>-2.9172</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.972</v>
+        <v>-0.5812</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9132</v>
+        <v>-2.336</v>
       </c>
       <c r="J21" t="n">
-        <v>3.411</v>
+        <v>-1.6071</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3096</v>
+        <v>-0.3292</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1015</v>
+        <v>-1.2779</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4698</v>
+        <v>-1.3101</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2816</v>
+        <v>-0.252</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1882</v>
+        <v>-1.0581</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1716</v>
+        <v>0.3964</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.9966</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0696</v>
+        <v>-0.9194</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7746</v>
+        <v>-0.0772</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4142</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3072</v>
+        <v>-5.4854</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7214</v>
+        <v>0.3803</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5858</v>
+        <v>-5.8657</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9172</v>
+        <v>-0.0588</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5812</v>
+        <v>-1.972</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.336</v>
+        <v>1.9132</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6071</v>
+        <v>3.411</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3292</v>
+        <v>0.3096</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2779</v>
+        <v>3.1015</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3101</v>
+        <v>-3.4698</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.252</v>
+        <v>-2.2816</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0581</v>
+        <v>-1.1882</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3964</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9757</v>
+        <v>-1.048</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1232</v>
+        <v>-0.2734</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1474</v>
+        <v>-0.7746</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8107</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.328799999999999</v>
+        <v>-9.571099999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0876</v>
+        <v>-4.1895</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.2412</v>
+        <v>-5.3816</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4392</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-1.015</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0552</v>
+        <v>-0.0467</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8279</v>
+        <v>-0.9683</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9364</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.0426</v>
+        <v>-10.1902</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.549</v>
+        <v>-3.7527</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.4936</v>
+        <v>-6.4374</v>
       </c>
       <c r="G24" t="n">
         <v>-6.3868</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4418</v>
+        <v>-1.5894</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5688</v>
+        <v>-0.7726</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.873</v>
+        <v>-0.8169</v>
       </c>
       <c r="V24" t="n">
         <v>-2.6104</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.4</v>
+        <v>-10.874</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.323</v>
+        <v>-8.6286</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.077</v>
+        <v>-2.2455</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4362</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4464</v>
+        <v>-0.9204</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6312</v>
+        <v>-0.9368</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1848</v>
+        <v>0.0164</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9405</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-46.52999999999999</v>
+        <v>-46.5299</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.4072</v>
+        <v>-18.407</v>
       </c>
       <c r="F26" t="n">
         <v>-28.1228</v>
@@ -2482,10 +2482,10 @@
         <v>10.9023</v>
       </c>
       <c r="S26" t="n">
-        <v>-10.2782</v>
+        <v>-10.2781</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.284800000000001</v>
+        <v>-5.2849</v>
       </c>
       <c r="U26" t="n">
         <v>-4.9935</v>
